--- a/output/full_scan/batch_seq8_2026-07-31.xlsx
+++ b/output/full_scan/batch_seq8_2026-07-31.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O125"/>
+  <dimension ref="A1:O129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.839997958640254</v>
+        <v>1.839997958640253</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>7805</v>
+        <v>6969</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>504.7891634361851</v>
+        <v>507.5806789493119</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>606</v>
+        <v>32.15</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>40.61750127736236</v>
+        <v>56.88011281381976</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>38.35224363672314</v>
+        <v>21.12559711687475</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.9064411574962884</v>
+        <v>0.6266311596740394</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.296523259805113</v>
+        <v>0.2476164362680384</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending</t>
+          <t>rsi_strong, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7828</v>
+        <v>7805</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>497.2974138026158</v>
+        <v>504.7891634361851</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1340</v>
+        <v>606</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,49 +1188,49 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>36.67412965552272</v>
+        <v>40.61750127736236</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>21.39804930314473</v>
+        <v>38.35224363672314</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.245617968750801</v>
+        <v>0.9064411574962884</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-89.71373829327024</v>
+        <v>0.296523259805113</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6855</v>
+        <v>7828</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>472.0671240564505</v>
+        <v>497.2974138026158</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>117</v>
+        <v>1340</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,49 +1241,49 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>51.80261116926949</v>
+        <v>36.67412965552272</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>6.705118897967965</v>
+        <v>21.39804930314473</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.1702092533740558</v>
+        <v>1.245617968750801</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.064301991815481</v>
+        <v>-89.71373829327024</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6949</v>
+        <v>6855</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>470.1575097082351</v>
+        <v>472.0671240564505</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>796</v>
+        <v>117</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>38.19205568634682</v>
+        <v>51.80261116926949</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>31.9342583297146</v>
+        <v>6.705118897967965</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.5944804121846754</v>
+        <v>0.1702092533740558</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-32.74615748841997</v>
+        <v>1.064301991815481</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>7795</v>
+        <v>6949</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>465.4521584981184</v>
+        <v>470.1575097082351</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>350.5</v>
+        <v>796</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>35.38680161875571</v>
+        <v>38.19205568634682</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>28.23131366531154</v>
+        <v>31.9342583297146</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.9247044715638399</v>
+        <v>0.5944804121846754</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-22.70132346692145</v>
+        <v>-32.74615748841997</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7788</v>
+        <v>7795</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>456.1873041865349</v>
+        <v>465.4521584981184</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>189.5</v>
+        <v>350.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>36.5103545186736</v>
+        <v>35.38680161875571</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>26.31538605044296</v>
+        <v>28.23131366531154</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.4515438380900624</v>
+        <v>0.9247044715638399</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-7.711549863766386</v>
+        <v>-22.70132346692145</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1428,21 +1428,21 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6922</v>
+        <v>7788</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>453.4930297243741</v>
+        <v>456.1873041865349</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>170</v>
+        <v>189.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>44.37075749176078</v>
+        <v>36.5103545186736</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>15.02604696010079</v>
+        <v>26.31538605044296</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.8306245881664341</v>
+        <v>0.4515438380900624</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-1.185602851560614</v>
+        <v>-7.711549863766386</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8040</v>
+        <v>6922</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>449.0344562281507</v>
+        <v>453.4930297243741</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>66</v>
+        <v>170</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>32.38562019815527</v>
+        <v>44.37075749176078</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>30.31056211005718</v>
+        <v>15.02604696010079</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.5922935328517057</v>
+        <v>0.8306245881664341</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-1.575165833672314</v>
+        <v>-1.185602851560614</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>7792</v>
+        <v>8040</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>447.7324998801438</v>
+        <v>449.0344562281507</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>191.5</v>
+        <v>66</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>32.80842410514113</v>
+        <v>32.38562019815527</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>36.9847515720142</v>
+        <v>30.31056211005718</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.056059036322896</v>
+        <v>0.5922935328517057</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-1.965752029689142</v>
+        <v>-1.575165833672314</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6903</v>
+        <v>7792</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>436.1473697690476</v>
+        <v>447.7324998801438</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>297</v>
+        <v>191.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>35.31022445540746</v>
+        <v>32.80842410514113</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>21.84676449381087</v>
+        <v>36.9847515720142</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.5553704600460699</v>
+        <v>1.056059036322896</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-9.185816980782617</v>
+        <v>-1.965752029689142</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8044</v>
+        <v>8033</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>435.3488180119121</v>
+        <v>440.0413764219364</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>25.6</v>
+        <v>165</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,49 +1665,49 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>38.59824405581952</v>
+        <v>42.69938389485068</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>19.20084530848977</v>
+        <v>29.02503217633949</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.6310714517367404</v>
+        <v>0.1121864454340802</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.1086257707621131</v>
+        <v>-10.13929495068141</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8016</v>
+        <v>6903</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>430.1537076403343</v>
+        <v>436.1473697690476</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>266.5</v>
+        <v>297</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,25 +1718,25 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>39.15024491334871</v>
+        <v>35.31022445540746</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>20.65566286163803</v>
+        <v>21.84676449381087</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.9598023335306032</v>
+        <v>0.5553704600460699</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-5.798904653741055</v>
+        <v>-9.185816980782617</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6870</v>
+        <v>8044</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>428.8961119170826</v>
+        <v>435.3488180119121</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>246.5</v>
+        <v>25.6</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>43.07046528381805</v>
+        <v>38.59824405581952</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>21.02918071071549</v>
+        <v>19.20084530848977</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.8644029777694472</v>
+        <v>0.6310714517367404</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-8.081848181975417</v>
+        <v>-0.1086257707621131</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>7747</v>
+        <v>8016</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>423.4746660913306</v>
+        <v>430.1537076403343</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>116</v>
+        <v>266.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>50.88622629048149</v>
+        <v>39.15024491334871</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>20.82836512693041</v>
+        <v>20.65566286163803</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.2809272981579025</v>
+        <v>0.9598023335306032</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-1.956416740704157</v>
+        <v>-5.798904653741055</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>7749</v>
+        <v>6870</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>421.6025782489181</v>
+        <v>428.8961119170826</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>320</v>
+        <v>246.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>28.8572846452733</v>
+        <v>43.07046528381805</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>36.15577468538934</v>
+        <v>21.02918071071549</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.9043605378820134</v>
+        <v>0.8644029777694472</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-3.954297068238525</v>
+        <v>-8.081848181975417</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6947</v>
+        <v>7747</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>台鎔科技</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>421.0411265546917</v>
+        <v>423.4746660913306</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>69.2</v>
+        <v>116</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>29.25531187680993</v>
+        <v>50.88622629048149</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>21.72110906790778</v>
+        <v>20.82836512693041</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.4169283924611223</v>
+        <v>0.2809272981579025</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-1.335553133615146</v>
+        <v>-1.956416740704157</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6944</v>
+        <v>7749</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>420.6804521800634</v>
+        <v>421.6025782489181</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>721</v>
+        <v>320</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>34.37084904471352</v>
+        <v>28.8572846452733</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>24.93136550243564</v>
+        <v>36.15577468538934</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.8617203081561066</v>
+        <v>0.9043605378820134</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-33.21471036776136</v>
+        <v>-3.954297068238525</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7839</v>
+        <v>6947</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>台鎔科技</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>420.557245168189</v>
+        <v>421.0411265546917</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>45.55</v>
+        <v>69.2</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>48.19729048008185</v>
+        <v>29.25531187680993</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>10.85103154058697</v>
+        <v>21.72110906790778</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.909075786539988</v>
+        <v>0.4169283924611223</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.4968823416209915</v>
+        <v>-1.335553133615146</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6952</v>
+        <v>6944</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>411.7787242378108</v>
+        <v>420.6804521800634</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>35.65</v>
+        <v>721</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>52.44349360108681</v>
+        <v>34.37084904471352</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>25.16766345857798</v>
+        <v>24.93136550243564</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>3.553174367265266</v>
+        <v>0.8617203081561066</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.0377073254835254</v>
+        <v>-33.21471036776136</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6877</v>
+        <v>7839</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>411.1186687416782</v>
+        <v>420.557245168189</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>112</v>
+        <v>45.55</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>38.47575618144565</v>
+        <v>48.19729048008185</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>22.47865802589904</v>
+        <v>10.85103154058697</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.5557456418365515</v>
+        <v>1.909075786539988</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-1.638921649465512</v>
+        <v>0.4968823416209915</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7772</v>
+        <v>6952</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>409.2556105956042</v>
+        <v>411.7787242378108</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>84.09999999999999</v>
+        <v>35.65</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>24.96480509116478</v>
+        <v>52.44349360108681</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>30.42296416757593</v>
+        <v>25.16766345857798</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.6229290921139828</v>
+        <v>3.553174367265266</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.6103907930254415</v>
+        <v>-0.0377073254835254</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7768</v>
+        <v>6877</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>404.7211472942981</v>
+        <v>411.1186687416782</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>252</v>
+        <v>112</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>28.20129856788786</v>
+        <v>38.47575618144565</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>42.03144538146441</v>
+        <v>22.47865802589904</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.9107104311985654</v>
+        <v>0.5557456418365515</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-5.503879446173819</v>
+        <v>-1.638921649465512</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>7717</v>
+        <v>7772</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>399.7701982044578</v>
+        <v>409.2556105956042</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>357</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>34.90573292472909</v>
+        <v>24.96480509116478</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>29.22250221310978</v>
+        <v>30.42296416757593</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.7411519864147436</v>
+        <v>0.6229290921139828</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-5.720790333654776</v>
+        <v>-0.6103907930254415</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6937</v>
+        <v>7768</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>396.4158829429095</v>
+        <v>404.7211472942981</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>44.77431512945954</v>
+        <v>28.20129856788786</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>12.42229346267745</v>
+        <v>42.03144538146441</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5489577888957419</v>
+        <v>0.9107104311985654</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-2.615359021688696</v>
+        <v>-5.503879446173819</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6953</v>
+        <v>7717</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>393.2808188289087</v>
+        <v>399.7701982044578</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>205</v>
+        <v>357</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>40.50496803303768</v>
+        <v>34.90573292472909</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>13.39101609668391</v>
+        <v>29.22250221310978</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.8398954250930727</v>
+        <v>0.7411519864147436</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-2.205696419336933</v>
+        <v>-5.720790333654776</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7711</v>
+        <v>6937</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>390.1217370154706</v>
+        <v>396.4158829429095</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>292.5</v>
+        <v>254</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>40.31520923409765</v>
+        <v>44.77431512945954</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>37.21487830879285</v>
+        <v>12.42229346267745</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.7586041940414989</v>
+        <v>0.5489577888957419</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.1950165403891759</v>
+        <v>-2.615359021688696</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>7721</v>
+        <v>6953</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>383.1989662908657</v>
+        <v>393.2808188289087</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>58.2</v>
+        <v>205</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>34.32861044831149</v>
+        <v>40.50496803303768</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>25.95419543685208</v>
+        <v>13.39101609668391</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.8397856973011532</v>
+        <v>0.8398954250930727</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.56804930800384</v>
+        <v>-2.205696419336933</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8021</v>
+        <v>7711</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>380.2325913313937</v>
+        <v>390.1217370154706</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>323</v>
+        <v>292.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>34.88427774942093</v>
+        <v>40.31520923409765</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>26.73045823390781</v>
+        <v>37.21487830879285</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.1874450154276847</v>
+        <v>0.7586041940414989</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-16.63700158408899</v>
+        <v>-0.1950165403891759</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8024</v>
+        <v>7721</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>378.6149575433187</v>
+        <v>383.1989662908657</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>14</v>
+        <v>58.2</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>42.9613356359699</v>
+        <v>34.32861044831149</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>24.30915142037021</v>
+        <v>25.95419543685208</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.3596491910067257</v>
+        <v>0.8397856973011532</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.3944351586360691</v>
+        <v>-0.56804930800384</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>7728</v>
+        <v>8021</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>368.8664894938949</v>
+        <v>380.2325913313937</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>544</v>
+        <v>323</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>33.9895632729702</v>
+        <v>34.88427774942093</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>21.05332045963011</v>
+        <v>26.73045823390781</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.585963382376682</v>
+        <v>0.1874450154276847</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-11.10476060353999</v>
+        <v>-16.63700158408899</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8042</v>
+        <v>8024</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>365.5842328179039</v>
+        <v>378.6149575433187</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>98.7</v>
+        <v>14</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>34.75157822169196</v>
+        <v>42.9613356359699</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>28.62752915169956</v>
+        <v>24.30915142037021</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.1195538448842723</v>
+        <v>0.3596491910067257</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-5.418242137621894</v>
+        <v>-0.3944351586360691</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6861</v>
+        <v>7610</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>362.8466197982598</v>
+        <v>376.010930953453</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>191</v>
+        <v>1200</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>31.29573176879954</v>
+        <v>30.36723748417727</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>32.16177719577039</v>
+        <v>34.46520073505844</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.1774591236752337</v>
+        <v>0.1160822281528798</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-2.552929326376187</v>
+        <v>-147.6848313029869</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>7547</v>
+        <v>7728</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>358.1432329191803</v>
+        <v>368.8664894938949</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>45.8</v>
+        <v>544</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>25.08122118311693</v>
+        <v>33.9895632729702</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>26.4544635082314</v>
+        <v>21.05332045963011</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.4510148955963282</v>
+        <v>1.585963382376682</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.7692076702772663</v>
+        <v>-11.10476060353999</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6885</v>
+        <v>8042</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>355.4667070782336</v>
+        <v>365.5842328179039</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>20.95</v>
+        <v>98.7</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>45.66111638766044</v>
+        <v>34.75157822169196</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>10.57081328801624</v>
+        <v>28.62752915169956</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5099172307299278</v>
+        <v>0.1195538448842723</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0143976611215952</v>
+        <v>-5.418242137621894</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6887</v>
+        <v>6861</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>353.2837641468246</v>
+        <v>362.8466197982598</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>36.6</v>
+        <v>191</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>50.01064821253507</v>
+        <v>31.29573176879954</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>14.9309224680141</v>
+        <v>32.16177719577039</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.0882385527294598</v>
+        <v>0.1774591236752337</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.130288579686123</v>
+        <v>-2.552929326376187</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6862</v>
+        <v>7547</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>353.2600669399419</v>
+        <v>358.1432329191803</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>125</v>
+        <v>45.8</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>31.50675434986648</v>
+        <v>25.08122118311693</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>26.70611724148062</v>
+        <v>26.4544635082314</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.5184607806482687</v>
+        <v>0.4510148955963282</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-3.51393739033761</v>
+        <v>-0.7692076702772663</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6965</v>
+        <v>6885</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>353.0731146960388</v>
+        <v>355.4667070782336</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>79.2</v>
+        <v>20.95</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>51.33096485630095</v>
+        <v>45.66111638766044</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>29.78063127580241</v>
+        <v>10.57081328801624</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.5240159036416695</v>
+        <v>0.5099172307299278</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.0024389524454408</v>
+        <v>0.0143976611215952</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>7722</v>
+        <v>6887</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>346.5403277434455</v>
+        <v>353.2837641468246</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>270</v>
+        <v>36.6</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>36.87165129544369</v>
+        <v>50.01064821253507</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>23.37621027529562</v>
+        <v>14.9309224680141</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.7847181156464841</v>
+        <v>0.0882385527294598</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-4.988554820758297</v>
+        <v>-0.130288579686123</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>7712</v>
+        <v>6862</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>346.056098338861</v>
+        <v>353.2600669399419</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>126.5</v>
+        <v>125</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>34.64942582432933</v>
+        <v>31.50675434986648</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>29.95236237738118</v>
+        <v>26.70611724148062</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.8476141671159009</v>
+        <v>0.5184607806482687</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-4.44793384683692</v>
+        <v>-3.51393739033761</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6913</v>
+        <v>6965</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>345.152322583175</v>
+        <v>353.0731146960388</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>120.5</v>
+        <v>79.2</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>46.07921210670595</v>
+        <v>51.33096485630095</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>14.25432905945698</v>
+        <v>29.78063127580241</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.5170181953512455</v>
+        <v>0.5240159036416695</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.5024422704335627</v>
+        <v>0.0024389524454408</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, williams_r_recovery</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6894</v>
+        <v>7722</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>344.4952344678172</v>
+        <v>346.5403277434455</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>323</v>
+        <v>270</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>44.55588727555678</v>
+        <v>36.87165129544369</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>19.8400898446205</v>
+        <v>23.37621027529562</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.898798174563353</v>
+        <v>0.7847181156464841</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-2.211928310742325</v>
+        <v>-4.988554820758297</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6921</v>
+        <v>7712</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>338.1304790945695</v>
+        <v>346.056098338861</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>59.3</v>
+        <v>126.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>32.23682585301064</v>
+        <v>34.64942582432933</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>30.17603527368902</v>
+        <v>29.95236237738118</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.567553380632271</v>
+        <v>0.8476141671159009</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.472959278978613</v>
+        <v>-4.44793384683692</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6936</v>
+        <v>6913</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>327.6437664199648</v>
+        <v>345.152322583175</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>31.8</v>
+        <v>120.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>41.47947642878946</v>
+        <v>46.07921210670595</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>15.35808829582305</v>
+        <v>14.25432905945698</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.0652446153446439</v>
+        <v>0.5170181953512455</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0123960216652191</v>
+        <v>-0.5024422704335627</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6994</v>
+        <v>6894</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>326.2219761996097</v>
+        <v>344.4952344678172</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>36.7</v>
+        <v>323</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>27.16595291601739</v>
+        <v>44.55588727555678</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>33.12528009399539</v>
+        <v>19.8400898446205</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5629883087654003</v>
+        <v>1.898798174563353</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.2228900190631879</v>
+        <v>-2.211928310742325</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6962</v>
+        <v>6921</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>322.6240643403249</v>
+        <v>338.1304790945695</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>30.95</v>
+        <v>59.3</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>37.73754772267812</v>
+        <v>32.23682585301064</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>28.92008903440443</v>
+        <v>30.17603527368902</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5842355613424781</v>
+        <v>1.567553380632271</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.3749239791710745</v>
+        <v>-0.472959278978613</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>7740</v>
+        <v>6936</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>315.5115717493633</v>
+        <v>327.6437664199648</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>141</v>
+        <v>31.8</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>41.33164958942256</v>
+        <v>41.47947642878946</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>15.02679140993481</v>
+        <v>15.35808829582305</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.8325634045099687</v>
+        <v>0.0652446153446439</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-1.050514441102705</v>
+        <v>0.0123960216652191</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6928</v>
+        <v>6994</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>314.1886007300681</v>
+        <v>326.2219761996097</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>48</v>
+        <v>36.7</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>44.90792708325988</v>
+        <v>27.16595291601739</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>23.2378647250532</v>
+        <v>33.12528009399539</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.1869649036733349</v>
+        <v>0.5629883087654003</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-1.086473684475696</v>
+        <v>0.2228900190631879</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>7821</v>
+        <v>6962</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>312.4701959277232</v>
+        <v>322.6240643403249</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>39.95</v>
+        <v>30.95</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>38.17396490765645</v>
+        <v>37.73754772267812</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>20.31801878360112</v>
+        <v>28.92008903440443</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6889329558726983</v>
+        <v>0.5842355613424781</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0648067387185433</v>
+        <v>-0.3749239791710745</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>7730</v>
+        <v>7740</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>311.5721511823938</v>
+        <v>315.5115717493633</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>37.66559009775701</v>
+        <v>41.33164958942256</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>25.60976182522506</v>
+        <v>15.02679140993481</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.8529678475325579</v>
+        <v>0.8325634045099687</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-2.844877749119478</v>
+        <v>-1.050514441102705</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>7822</v>
+        <v>6928</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>305.1968007661564</v>
+        <v>314.1886007300681</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>770</v>
+        <v>48</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>32.76170638389715</v>
+        <v>44.90792708325988</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>26.46937548936322</v>
+        <v>23.2378647250532</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.9457626595886952</v>
+        <v>0.1869649036733349</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-11.80122429977435</v>
+        <v>-1.086473684475696</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6931</v>
+        <v>7821</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>304.9563623077595</v>
+        <v>312.4701959277232</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>37.5</v>
+        <v>39.95</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>36.16691961478272</v>
+        <v>38.17396490765645</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>15.74282265863936</v>
+        <v>20.31801878360112</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.656686832716844</v>
+        <v>0.6889329558726983</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.1859332278078321</v>
+        <v>0.0648067387185433</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6899</v>
+        <v>7730</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>304.209250992718</v>
+        <v>311.5721511823938</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>49.95</v>
+        <v>151</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>32.27572443931668</v>
+        <v>37.66559009775701</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>28.07569711803715</v>
+        <v>25.60976182522506</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5903609764783787</v>
+        <v>0.8529678475325579</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.11162860867557</v>
+        <v>-2.844877749119478</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>7827</v>
+        <v>7822</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>303.7573949020158</v>
+        <v>305.1968007661564</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>142.5</v>
+        <v>770</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>39.88743632790728</v>
+        <v>32.76170638389715</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>20.85842671999215</v>
+        <v>26.46937548936322</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.3854484381189718</v>
+        <v>0.9457626595886952</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-2.514656767279127</v>
+        <v>-11.80122429977435</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>7703</v>
+        <v>6931</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>302.3980851427816</v>
+        <v>304.9563623077595</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>162</v>
+        <v>37.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>33.75690190275371</v>
+        <v>36.16691961478272</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>23.72238513144704</v>
+        <v>15.74282265863936</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.2597729781497421</v>
+        <v>1.656686832716844</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-3.367392797331007</v>
+        <v>-0.1859332278078321</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6906</v>
+        <v>6899</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>302.1274316775642</v>
+        <v>304.209250992718</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>68.2</v>
+        <v>49.95</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>28.02816672419515</v>
+        <v>32.27572443931668</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>31.87430080984736</v>
+        <v>28.07569711803715</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5611528595173421</v>
+        <v>0.5903609764783787</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.3073560854634412</v>
+        <v>-0.11162860867557</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>7556</v>
+        <v>7827</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>300.9716084458162</v>
+        <v>303.7573949020158</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>210</v>
+        <v>142.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>35.30162489698351</v>
+        <v>39.88743632790728</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>37.3349520088555</v>
+        <v>20.85842671999215</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.4698240137695566</v>
+        <v>0.3854484381189718</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-2.201021007416442</v>
+        <v>-2.514656767279127</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>7732</v>
+        <v>7703</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>297.4055210627636</v>
+        <v>302.3980851427816</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>35.65</v>
+        <v>162</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>51.75208345697101</v>
+        <v>33.75690190275371</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>5.162323980315694</v>
+        <v>23.72238513144704</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.611877133808094</v>
+        <v>0.2597729781497421</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.1040620280401802</v>
+        <v>-3.367392797331007</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>7786</v>
+        <v>6906</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>294.249431743003</v>
+        <v>302.1274316775642</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>126.5</v>
+        <v>68.2</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>49.25177862643166</v>
+        <v>28.02816672419515</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>14.57862877388011</v>
+        <v>31.87430080984736</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.8814368187813084</v>
+        <v>0.5611528595173421</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.7267044217603169</v>
+        <v>-0.3073560854634412</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>7704</v>
+        <v>7556</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>289.7183647258958</v>
+        <v>300.9716084458162</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>54.3</v>
+        <v>210</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>44.34658414889034</v>
+        <v>35.30162489698351</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>26.8052515679876</v>
+        <v>37.3349520088555</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.427490187105064</v>
+        <v>0.4698240137695566</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.1278547361447342</v>
+        <v>-2.201021007416442</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4237,21 +4237,21 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6955</v>
+        <v>7732</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>289.3000048806414</v>
+        <v>297.4055210627636</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>114</v>
+        <v>35.65</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>48.06325219596966</v>
+        <v>51.75208345697101</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>6.096709919916353</v>
+        <v>5.162323980315694</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>2.11870014261114</v>
+        <v>1.611877133808094</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.7787780304806962</v>
+        <v>-0.1040620280401802</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>7791</v>
+        <v>7786</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>288.2135642686366</v>
+        <v>294.249431743003</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>60</v>
+        <v>126.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>31.0688820000565</v>
+        <v>49.25177862643166</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>20.92572304053706</v>
+        <v>14.57862877388011</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6424422113782163</v>
+        <v>0.8814368187813084</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.2455363672755598</v>
+        <v>-0.7267044217603169</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8034</v>
+        <v>7704</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>283.6133474396121</v>
+        <v>289.7183647258958</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>18.4</v>
+        <v>54.3</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>30.45325750138288</v>
+        <v>44.34658414889034</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>39.07485243664281</v>
+        <v>26.8052515679876</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.3368832367220386</v>
+        <v>1.427490187105064</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.09139665563224431</v>
+        <v>-0.1278547361447342</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>7631</v>
+        <v>6955</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>282.1891884586612</v>
+        <v>289.3000048806414</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>45.5538524262952</v>
+        <v>48.06325219596966</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>11.31821914411434</v>
+        <v>6.096709919916353</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5737615602303512</v>
+        <v>2.11870014261114</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-2.074489402684042</v>
+        <v>0.7787780304806962</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6910</v>
+        <v>7791</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>281.7382469332326</v>
+        <v>288.2135642686366</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>24.4</v>
+        <v>60</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>35.43453567682248</v>
+        <v>31.0688820000565</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>31.4278756204118</v>
+        <v>20.92572304053706</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.5552593864453015</v>
+        <v>0.6424422113782163</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0518931749240993</v>
+        <v>-0.2455363672755598</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4502,21 +4502,21 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6916</v>
+        <v>8034</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>280.9413510342046</v>
+        <v>283.6133474396121</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>17.9</v>
+        <v>18.4</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>39.21373719438057</v>
+        <v>30.45325750138288</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>16.67044258922667</v>
+        <v>39.07485243664281</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.5152586832798557</v>
+        <v>0.3368832367220386</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.305423759539046</v>
+        <v>-0.09139665563224431</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6996</v>
+        <v>7631</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>279.0861152724437</v>
+        <v>282.1891884586612</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>42.98189545866679</v>
+        <v>45.5538524262952</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>25.67297805249994</v>
+        <v>11.31821914411434</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.4464069993985534</v>
+        <v>0.5737615602303512</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.84702075929507</v>
+        <v>-2.074489402684042</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>7744</v>
+        <v>6910</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>274.2062093785792</v>
+        <v>281.7382469332326</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>400.5</v>
+        <v>24.4</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>38.73338142924349</v>
+        <v>35.43453567682248</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>22.34162075148745</v>
+        <v>31.4278756204118</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.4019917566054368</v>
+        <v>0.5552593864453015</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-4.048462748583908</v>
+        <v>-0.0518931749240993</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>7689</v>
+        <v>6916</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>大鵬科CLMX</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>273.8812388007986</v>
+        <v>280.9413510342046</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>176</v>
+        <v>17.9</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>22.26512742536679</v>
+        <v>39.21373719438057</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>26.91294308740798</v>
+        <v>16.67044258922667</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.47918832615476</v>
+        <v>0.5152586832798557</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-4.362490471458813</v>
+        <v>-0.305423759539046</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>7751</v>
+        <v>6996</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>272.4834046647427</v>
+        <v>279.0861152724437</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>1230</v>
+        <v>173</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>47.64520013897404</v>
+        <v>42.98189545866679</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>16.98329146291658</v>
+        <v>25.67297805249994</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.12546895547018</v>
+        <v>0.4464069993985534</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>1</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>9.045921692511456</v>
+        <v>-0.84702075929507</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>7799</v>
+        <v>7744</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>265.6733363203316</v>
+        <v>274.2062093785792</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>348.5</v>
+        <v>400.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>39.09846588217651</v>
+        <v>38.73338142924349</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>24.26336915163256</v>
+        <v>22.34162075148745</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.3511719496391737</v>
+        <v>0.4019917566054368</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-10.9156795180513</v>
+        <v>-4.048462748583908</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6933</v>
+        <v>7689</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>大鵬科CLMX</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>261.6220965829877</v>
+        <v>273.8812388007986</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>46.45367023232281</v>
+        <v>22.26512742536679</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>15.0782447132416</v>
+        <v>26.91294308740798</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.7903778587382175</v>
+        <v>1.47918832615476</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-1.987767553738704</v>
+        <v>-4.362490471458813</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6924</v>
+        <v>8028</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>261.3070116167119</v>
+        <v>273.8136059815381</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>103</v>
+        <v>245</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>39.54869353585481</v>
+        <v>37.50672159600581</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>23.70005909318648</v>
+        <v>19.31620002873514</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.01038592532406</v>
+        <v>0.225564070196041</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.680466262502514</v>
+        <v>-8.885194856923484</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6854</v>
+        <v>7751</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>260.9282504304715</v>
+        <v>272.4834046647427</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>91.09999999999999</v>
+        <v>1230</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>30.98735482412353</v>
+        <v>47.64520013897404</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>45.5931006450553</v>
+        <v>16.98329146291658</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.5696956799319004</v>
+        <v>1.12546895547018</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.7916085883574997</v>
+        <v>9.045921692511456</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6918</v>
+        <v>7799</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>258.7105256439524</v>
+        <v>265.6733363203316</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>71.59999999999999</v>
+        <v>348.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>45.75397836489128</v>
+        <v>39.09846588217651</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>15.97402570385587</v>
+        <v>24.26336915163256</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.6177786073456992</v>
+        <v>0.3511719496391737</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.2530193409893201</v>
+        <v>-10.9156795180513</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>7769</v>
+        <v>6933</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>253.0041408567013</v>
+        <v>261.6220965829877</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>6180</v>
+        <v>150</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>48.29863904816859</v>
+        <v>46.45367023232281</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>16.72591851425824</v>
+        <v>15.0782447132416</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.3777422263194775</v>
+        <v>0.7903778587382175</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-48.92365572315396</v>
+        <v>-1.987767553738704</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>7736</v>
+        <v>6924</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>250.940661021342</v>
+        <v>261.3070116167119</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>70.40000000000001</v>
+        <v>103</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>45.91197388168772</v>
+        <v>39.54869353585481</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>25.88156486471826</v>
+        <v>23.70005909318648</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.4940661021341929</v>
+        <v>1.01038592532406</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.08705883363719789</v>
+        <v>-0.680466262502514</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>7810</v>
+        <v>6854</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>249.5420451634087</v>
+        <v>260.9282504304715</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>177</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>31.1995604172043</v>
+        <v>30.98735482412353</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>16.09554549553521</v>
+        <v>45.5931006450553</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.363579400420127</v>
+        <v>0.5696956799319004</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-2.040829580038088</v>
+        <v>-0.7916085883574997</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6925</v>
+        <v>6918</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>248.6427023146248</v>
+        <v>258.7105256439524</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>51.1</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>33.98857943701411</v>
+        <v>45.75397836489128</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>17.81912886918226</v>
+        <v>15.97402570385587</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.8927589737918596</v>
+        <v>0.6177786073456992</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.4152470862473194</v>
+        <v>-0.2530193409893201</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>7842</v>
+        <v>7769</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>248.0882123473558</v>
+        <v>253.0041408567013</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>79.90000000000001</v>
+        <v>6180</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>45.11183167936099</v>
+        <v>48.29863904816859</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>11.77396175786912</v>
+        <v>16.72591851425824</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.216773388242116</v>
+        <v>0.3777422263194775</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.2732294477591974</v>
+        <v>-48.92365572315396</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8032</v>
+        <v>7736</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>245.6683136515611</v>
+        <v>250.940661021342</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>34.6</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>33.05930114214294</v>
+        <v>45.91197388168772</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>35.71321479344341</v>
+        <v>25.88156486471826</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.6902739065254316</v>
+        <v>0.4940661021341929</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.3414291442523578</v>
+        <v>0.08705883363719789</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6869</v>
+        <v>7810</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>245.5253237478116</v>
+        <v>249.5420451634087</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>65.59999999999999</v>
+        <v>177</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>36.12748289767401</v>
+        <v>31.1995604172043</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>24.00799203065694</v>
+        <v>16.09554549553521</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.285254414138421</v>
+        <v>0.363579400420127</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0573970679582767</v>
+        <v>-2.040829580038088</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>7820</v>
+        <v>6925</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>244.3542265875365</v>
+        <v>248.6427023146248</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>100</v>
+        <v>51.1</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>31.76840227227027</v>
+        <v>33.98857943701411</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>23.35319201331324</v>
+        <v>17.81912886918226</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.6066319139028302</v>
+        <v>0.8927589737918596</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-1.072927924981689</v>
+        <v>-0.4152470862473194</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8011</v>
+        <v>7842</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>238.1762225461261</v>
+        <v>248.0882123473558</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>16.45</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>44.97329286587337</v>
+        <v>45.11183167936099</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>31.54995212672954</v>
+        <v>11.77396175786912</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.289543233273994</v>
+        <v>1.216773388242116</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0313835835120581</v>
+        <v>0.2732294477591974</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6951</v>
+        <v>8032</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>236.4925959400222</v>
+        <v>245.6683136515611</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>34.6</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>34.2749091144741</v>
+        <v>33.05930114214294</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>38.11571890645326</v>
+        <v>35.71321479344341</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.1958420184151088</v>
+        <v>0.6902739065254316</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0330612407696686</v>
+        <v>-0.3414291442523578</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5562,21 +5562,21 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>7818</v>
+        <v>6869</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>235.0963758899017</v>
+        <v>245.5253237478116</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>64.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>32.43845634858988</v>
+        <v>36.12748289767401</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>26.65522338146117</v>
+        <v>24.00799203065694</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.4373743256518185</v>
+        <v>1.285254414138421</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.3686314282170726</v>
+        <v>0.0573970679582767</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>7780</v>
+        <v>7820</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>233.4932336505266</v>
+        <v>244.3542265875365</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>16.8</v>
+        <v>100</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>34.08423073692518</v>
+        <v>31.76840227227027</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>30.57551080234468</v>
+        <v>23.35319201331324</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.53546341923931</v>
+        <v>0.6066319139028302</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0692719837361347</v>
+        <v>-1.072927924981689</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>7803</v>
+        <v>8011</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>229.1324446535272</v>
+        <v>238.1762225461261</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>19.8</v>
+        <v>16.45</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>34.45277522597002</v>
+        <v>44.97329286587337</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>24.24063214989096</v>
+        <v>31.54995212672954</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.2606400024415925</v>
+        <v>1.289543233273994</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.178682901177867</v>
+        <v>-0.0313835835120581</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>7738</v>
+        <v>6951</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>227.254431762602</v>
+        <v>236.4925959400222</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>165.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>44.43975159049833</v>
+        <v>34.2749091144741</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>26.4790788443727</v>
+        <v>38.11571890645326</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.8424922563276176</v>
+        <v>0.1958420184151088</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.2618511234588816</v>
+        <v>-0.0330612407696686</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5774,21 +5774,21 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>7715</v>
+        <v>7818</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>223.8965286087636</v>
+        <v>235.0963758899017</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>31.35</v>
+        <v>64.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>46.16924189163453</v>
+        <v>32.43845634858988</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>29.59421150516804</v>
+        <v>26.65522338146117</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.5296603626118389</v>
+        <v>0.4373743256518185</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.6433602676794657</v>
+        <v>-0.3686314282170726</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>7753</v>
+        <v>7780</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>221.8181102316112</v>
+        <v>233.4932336505266</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>37.35</v>
+        <v>16.8</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>35.8520507569487</v>
+        <v>34.08423073692518</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>18.19688863772709</v>
+        <v>30.57551080234468</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.3687115341489547</v>
+        <v>0.53546341923931</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.4505201867002051</v>
+        <v>-0.0692719837361347</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6909</v>
+        <v>7803</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>220.1351776376002</v>
+        <v>229.1324446535272</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>40.35</v>
+        <v>19.8</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>35.91664519922634</v>
+        <v>34.45277522597002</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>30.4302103168043</v>
+        <v>24.24063214989096</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.4557916690445979</v>
+        <v>0.2606400024415925</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.7046451571027337</v>
+        <v>-0.178682901177867</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6988</v>
+        <v>7738</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>216.5214875398788</v>
+        <v>227.254431762602</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>12.1</v>
+        <v>165.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>49.08360296026353</v>
+        <v>44.43975159049833</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>14.84586310801515</v>
+        <v>26.4790788443727</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.337969143417206</v>
+        <v>0.8424922563276176</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0056542376240394</v>
+        <v>-0.2618511234588816</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6983</v>
+        <v>7715</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>215.2331483626776</v>
+        <v>223.8965286087636</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>301.5</v>
+        <v>31.35</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>35.74844962189425</v>
+        <v>46.16924189163453</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>12.47257518493669</v>
+        <v>29.59421150516804</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.4981983994296248</v>
+        <v>0.5296603626118389</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-3.850460882450637</v>
+        <v>-0.6433602676794657</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6967</v>
+        <v>7753</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>211.3804283410751</v>
+        <v>221.8181102316112</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>68.2</v>
+        <v>37.35</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>41.23803940159078</v>
+        <v>35.8520507569487</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>16.89501549235042</v>
+        <v>18.19688863772709</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.301033387230024</v>
+        <v>0.3687115341489547</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.9603634856859372</v>
+        <v>-0.4505201867002051</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>7765</v>
+        <v>6909</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>208.4917056322636</v>
+        <v>220.1351776376002</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>225.5</v>
+        <v>40.35</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>47.32857200407249</v>
+        <v>35.91664519922634</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>14.35318833647344</v>
+        <v>30.4302103168043</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.5839937873773443</v>
+        <v>0.4557916690445979</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.6492348516279267</v>
+        <v>-0.7046451571027337</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6902</v>
+        <v>6988</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>202.0790412660498</v>
+        <v>216.5214875398788</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>121</v>
+        <v>12.1</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>44.96336544072596</v>
+        <v>49.08360296026353</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>19.85007196372584</v>
+        <v>14.84586310801515</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>2.24209194599409</v>
+        <v>0.337969143417206</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.7639344872023943</v>
+        <v>0.0056542376240394</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>7402</v>
+        <v>6983</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>193.3221693165801</v>
+        <v>215.2331483626776</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>102</v>
+        <v>301.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>42.70178021427608</v>
+        <v>35.74844962189425</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>23.35359861253986</v>
+        <v>12.47257518493669</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.1904709119638175</v>
+        <v>0.4981983994296248</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-3.742383174789038</v>
+        <v>-3.850460882450637</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>7705</v>
+        <v>6967</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>192.5592978037757</v>
+        <v>211.3804283410751</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>30.4</v>
+        <v>68.2</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>44.17722015900868</v>
+        <v>41.23803940159078</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>16.22724837136347</v>
+        <v>16.89501549235042</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4069358357406274</v>
+        <v>0.301033387230024</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0154829866850135</v>
+        <v>-0.9603634856859372</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>7770</v>
+        <v>7765</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>176.7979545026564</v>
+        <v>208.4917056322636</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>40.15</v>
+        <v>225.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>50.62164383019815</v>
+        <v>47.32857200407249</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>11.61886371192968</v>
+        <v>14.35318833647344</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.290910446266129</v>
+        <v>0.5839937873773443</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.1186884660775344</v>
+        <v>0.6492348516279267</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6890</v>
+        <v>6902</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>175.7911787357727</v>
+        <v>202.0790412660498</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>38.05551887347074</v>
+        <v>44.96336544072596</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>16.5504537086674</v>
+        <v>19.85007196372584</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.5794508333472372</v>
+        <v>2.24209194599409</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.2453651214254097</v>
+        <v>-0.7639344872023943</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6997</v>
+        <v>7402</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>169.972892757688</v>
+        <v>193.3221693165801</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>40.12489311151011</v>
+        <v>42.70178021427608</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>13.22798746348892</v>
+        <v>23.35359861253986</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.0248774420136094</v>
+        <v>0.1904709119638175</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-6.378818007417082</v>
+        <v>-3.742383174789038</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8038</v>
+        <v>7705</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>169.5054855273827</v>
+        <v>192.5592978037757</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>31.55</v>
+        <v>30.4</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>31.08393146242886</v>
+        <v>44.17722015900868</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>18.25300363923704</v>
+        <v>16.22724837136347</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.2193278766850132</v>
+        <v>0.4069358357406274</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.7753398130557996</v>
+        <v>-0.0154829866850135</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6859</v>
+        <v>7770</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>165.1784527179826</v>
+        <v>176.7979545026564</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>40.15</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>32.81717949634037</v>
+        <v>50.62164383019815</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>31.8103170261554</v>
+        <v>11.61886371192968</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.7963954871938721</v>
+        <v>0.290910446266129</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.1614382817471691</v>
+        <v>0.1186884660775344</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6908</v>
+        <v>6890</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>163.0820984466462</v>
+        <v>175.7911787357727</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>33.85</v>
+        <v>168</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>34.36718562200751</v>
+        <v>38.05551887347074</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>25.8983597697383</v>
+        <v>16.5504537086674</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.5325968244694448</v>
+        <v>0.5794508333472372</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.2353372539579465</v>
+        <v>-0.2453651214254097</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6873</v>
+        <v>6997</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>163.0662336566343</v>
+        <v>169.972892757688</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>78.3</v>
+        <v>0</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>39.92701934220774</v>
+        <v>40.12489311151011</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>15.78542853215275</v>
+        <v>13.22798746348892</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.6385590834212176</v>
+        <v>0.0248774420136094</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.94337337887243</v>
+        <v>-6.378818007417082</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6675,21 +6675,21 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6895</v>
+        <v>8038</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>157.2664788386107</v>
+        <v>169.5054855273827</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>118</v>
+        <v>31.55</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>33.28731165969897</v>
+        <v>31.08393146242886</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>32.37285431621984</v>
+        <v>18.25300363923704</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.6299052959773493</v>
+        <v>0.2193278766850132</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.319411894017799</v>
+        <v>-0.7753398130557996</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>7760</v>
+        <v>6859</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>151.1201904902505</v>
+        <v>165.1784527179826</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>34</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>47.4402729609136</v>
+        <v>32.81717949634037</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>21.07190630172411</v>
+        <v>31.8103170261554</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.7903049035300055</v>
+        <v>0.7963954871938721</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.1561700290598986</v>
+        <v>-0.1614382817471691</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6781,21 +6781,21 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>7823</v>
+        <v>6908</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>148.171162186871</v>
+        <v>163.0820984466462</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>80</v>
+        <v>33.85</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>43.01581341031405</v>
+        <v>34.36718562200751</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>20.86255480038896</v>
+        <v>25.8983597697383</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.6308328799555192</v>
+        <v>0.5325968244694448</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.405892827378689</v>
+        <v>-0.2353372539579465</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6834,21 +6834,21 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6934</v>
+        <v>6873</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>132.6798405694124</v>
+        <v>163.0662336566343</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>73</v>
+        <v>78.3</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>43.97712399494942</v>
+        <v>39.92701934220774</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>18.60795751140756</v>
+        <v>15.78542853215275</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.296346479227786</v>
+        <v>0.6385590834212176</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.7069883222847544</v>
+        <v>-0.94337337887243</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6887,21 +6887,21 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6923</v>
+        <v>6895</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>129.9741379206932</v>
+        <v>157.2664788386107</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>77.09999999999999</v>
+        <v>118</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>49.47604001704305</v>
+        <v>33.28731165969897</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>12.00211283442868</v>
+        <v>32.37285431621984</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.6145356365692853</v>
+        <v>0.6299052959773493</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.1620476651383574</v>
+        <v>-0.319411894017799</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6919</v>
+        <v>7760</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>106.246951981336</v>
+        <v>151.1201904902505</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>103</v>
+        <v>34</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>49.96312462372146</v>
+        <v>47.4402729609136</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>12.86408068696157</v>
+        <v>21.07190630172411</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.6493187948294494</v>
+        <v>0.7903049035300055</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.4699337925084982</v>
+        <v>-0.1561700290598986</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6971</v>
+        <v>7823</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>101.8398700335289</v>
+        <v>148.171162186871</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>25.85</v>
+        <v>80</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>34.58697198668327</v>
+        <v>43.01581341031405</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>15.86932735149547</v>
+        <v>20.86255480038896</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.4988028731045491</v>
+        <v>0.6308328799555192</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,62 +7036,274 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.1401408788995291</v>
+        <v>-0.405892827378689</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
+        <v>6934</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>心誠鎂</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>132.6798405694124</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>43.97712399494942</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>18.60795751140756</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.296346479227786</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>-0.7069883222847544</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>6923</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>中台</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>129.9741379206932</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>49.47604001704305</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>12.00211283442868</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.6145356365692853</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>-0.1620476651383574</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>6919</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>康霈*</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>106.246951981336</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>49.96312462372146</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>12.86408068696157</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.6493187948294494</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>-0.4699337925084982</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>6971</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>惠民實業</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>101.8398700335289</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>34.58697198668327</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>15.86932735149547</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0.4988028731045491</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>-0.1401408788995291</v>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
         <v>6865</v>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>偉康科技</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D125" s="2" t="n">
+      <c r="C129" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D129" s="2" t="n">
         <v>98.04695326714368</v>
       </c>
-      <c r="E125" s="2" t="n">
+      <c r="E129" s="2" t="n">
         <v>25.05</v>
       </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H125" s="2" t="n">
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" s="2" t="n">
         <v>51.23157058140191</v>
       </c>
-      <c r="I125" s="2" t="n">
+      <c r="I129" s="2" t="n">
         <v>10.47591425863181</v>
       </c>
-      <c r="J125" s="2" t="n">
+      <c r="J129" s="2" t="n">
         <v>0.6538668293887752</v>
       </c>
-      <c r="K125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N125" s="2" t="n">
+      <c r="K129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" s="2" t="n">
         <v>-0.492095959230334</v>
       </c>
-      <c r="O125" s="2" t="inlineStr">
+      <c r="O129" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
